--- a/产品要素表.xlsx
+++ b/产品要素表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1EFBCB-6793-4102-A863-CF3DE5D98BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DD87B8-65AD-4154-A609-3AFA68A67077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="45">
   <si>
     <t>产品名称</t>
   </si>
@@ -50,27 +50,156 @@
     <t>备注</t>
   </si>
   <si>
+    <t>元康盛景20号</t>
+  </si>
+  <si>
+    <t>直销</t>
+  </si>
+  <si>
     <t>代销</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直销</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元康盛景20号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>朗瑞1号5期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>朗瑞1号7期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>外贸信托-元康盛景1号</t>
+  </si>
+  <si>
+    <t>元康盛景28号</t>
+  </si>
+  <si>
+    <t>元康盛景26号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康盛景29号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慧聚领航1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏信添利2501优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏信添利2502次级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏信添利2603混合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康盛景1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康盛景9号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康盛景17号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗瑞1号6期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗瑞1号8期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹏雅10号119期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹏雅10号120期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昆银1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中建投臻泉2号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基金类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>母基金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子基金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康20号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏信优先级Z2501</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏信次级Z2502</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏信混合Z2603</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康9号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元康17号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗瑞1_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗瑞1_7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗瑞1_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗瑞1_8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹏雅119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹏雅120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中建投_臻泉2号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -418,113 +547,614 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" customWidth="1"/>
-    <col min="5" max="5" width="16.9296875" customWidth="1"/>
+    <col min="1" max="1" width="22.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/产品要素表.xlsx
+++ b/产品要素表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DD87B8-65AD-4154-A609-3AFA68A67077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBBE7B8-7F40-41CF-B6D8-9ED8F6520941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,7 +591,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -611,7 +611,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -691,7 +691,7 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -711,7 +711,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -731,7 +731,7 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -791,7 +791,7 @@
         <v>2</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -811,7 +811,7 @@
         <v>3</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -891,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -931,7 +931,7 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="s">
         <v>29</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="s">
         <v>29</v>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="s">
         <v>29</v>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="s">
         <v>29</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="s">
         <v>29</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="s">
         <v>29</v>

--- a/产品要素表.xlsx
+++ b/产品要素表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBBE7B8-7F40-41CF-B6D8-9ED8F6520941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97207730-00FB-478C-A095-3BB49DDC7853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -591,7 +591,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -611,7 +611,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -691,7 +691,7 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -711,7 +711,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -731,7 +731,7 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -791,7 +791,7 @@
         <v>2</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -811,7 +811,7 @@
         <v>3</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -891,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -931,7 +931,7 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="s">
         <v>29</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="s">
         <v>29</v>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
         <v>29</v>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" t="s">
         <v>29</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" t="s">
         <v>29</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="s">
         <v>29</v>
